--- a/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,71</t>
+          <t>-2,75; 4,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 6,47</t>
+          <t>-2,07; 6,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -0,77</t>
+          <t>-7,1; -0,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,67</t>
+          <t>-5,61; 0,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,71</t>
+          <t>-3,31; 0,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,13</t>
+          <t>-2,56; 2,44</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 310,98</t>
+          <t>-100,0; 334,93</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,2</t>
+          <t>-2,26; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,63</t>
+          <t>0,45; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,76</t>
+          <t>-2,21; 0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,14</t>
+          <t>1,01; 5,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,4</t>
+          <t>-1,85; 0,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,2</t>
+          <t>1,42; 4,48</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 66,75</t>
+          <t>-59,51; 77,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 226,95</t>
+          <t>8,84; 241,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 62,11</t>
+          <t>-70,9; 60,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,95; 333,64</t>
+          <t>27,04; 372,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 24,16</t>
+          <t>-55,77; 28,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,72; 206,98</t>
+          <t>41,91; 224,11</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,51</t>
+          <t>-3,2; 5,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,97</t>
+          <t>4,6; 17,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,99</t>
+          <t>1,09; 9,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,7</t>
+          <t>4,15; 14,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,91</t>
+          <t>0,03; 6,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,08</t>
+          <t>6,19; 14,29</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 128,13</t>
+          <t>-40,46; 132,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,66; 421,97</t>
+          <t>47,63; 402,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,55; 371,84</t>
+          <t>5,62; 352,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,45; 547,17</t>
+          <t>57,52; 548,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 170,05</t>
+          <t>-4,15; 159,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,37; 358,06</t>
+          <t>82,45; 337,97</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,66</t>
+          <t>-1,6; 1,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,63</t>
+          <t>2,33; 6,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,18</t>
+          <t>-0,64; 2,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,9</t>
+          <t>2,34; 6,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,37</t>
+          <t>-0,74; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,8</t>
+          <t>2,85; 5,66</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 63,35</t>
+          <t>-36,91; 63,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,84; 233,91</t>
+          <t>49,54; 234,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 101,61</t>
+          <t>-19,03; 119,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53,71; 284,37</t>
+          <t>62,15; 292,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 51,86</t>
+          <t>-20,57; 56,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,72; 222,06</t>
+          <t>80,63; 217,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,12</t>
+          <t>-2,73; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,18</t>
+          <t>-2,0; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -0,77</t>
+          <t>-6,35; -0,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,69</t>
+          <t>-5,69; 0,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,59</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,44</t>
+          <t>-2,49; 2,26</t>
         </is>
       </c>
     </row>
@@ -725,12 +725,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 376,09</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 334,93</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,31</t>
+          <t>-2,42; 1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,78</t>
+          <t>0,43; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,7</t>
+          <t>-2,27; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,29</t>
+          <t>1,03; 5,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,51</t>
+          <t>-1,89; 0,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,48</t>
+          <t>1,17; 4,35</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 77,22</t>
+          <t>-61,03; 68,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 241,52</t>
+          <t>6,14; 239,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 60,6</t>
+          <t>-71,88; 54,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,04; 372,51</t>
+          <t>25,56; 333,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 28,03</t>
+          <t>-57,22; 32,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,91; 224,11</t>
+          <t>34,66; 224,94</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,63</t>
+          <t>-3,58; 5,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 17,81</t>
+          <t>5,39; 17,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,99</t>
+          <t>1,47; 10,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 14,39</t>
+          <t>3,83; 14,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,54</t>
+          <t>0,1; 6,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 14,29</t>
+          <t>5,53; 13,77</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 132,63</t>
+          <t>-40,92; 128,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,63; 402,37</t>
+          <t>53,47; 405,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 352,05</t>
+          <t>15,54; 361,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57,52; 548,54</t>
+          <t>51,75; 493,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 159,44</t>
+          <t>-0,15; 161,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,45; 337,97</t>
+          <t>75,39; 327,6</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,7</t>
+          <t>-1,6; 1,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,55</t>
+          <t>2,41; 6,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,39</t>
+          <t>-0,73; 2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,17</t>
+          <t>2,21; 6,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,43</t>
+          <t>-0,71; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,66</t>
+          <t>2,79; 5,67</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 63,78</t>
+          <t>-36,68; 69,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,54; 234,57</t>
+          <t>51,96; 238,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 119,33</t>
+          <t>-20,85; 110,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62,15; 292,01</t>
+          <t>54,99; 270,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 56,18</t>
+          <t>-19,66; 59,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,63; 217,83</t>
+          <t>73,41; 224,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Estudios-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,13</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,2</t>
+          <t>-6,38; -0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,47</t>
+          <t>-5,59; 0,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,77</t>
+          <t>-2,55; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,55</t>
+          <t>-1,45; 8,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,62</t>
+          <t>-3,16; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,26</t>
+          <t>-2,32; 2,77</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-73,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-6,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>77,85%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-71,17%</t>
+          <t>123,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,01%</t>
+          <t>-7,07%</t>
         </is>
       </c>
     </row>
@@ -725,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 376,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 394,98</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,03</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,15</t>
+          <t>-2,09; 0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,88</t>
+          <t>1,19; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,68</t>
+          <t>-2,29; 1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,16</t>
+          <t>0,58; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,49</t>
+          <t>-1,73; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,35</t>
+          <t>1,57; 4,34</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-32,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>135,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-18,56%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-32,52%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136,69%</t>
+          <t>106,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>112,21%</t>
+          <t>119,81%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 68,29</t>
+          <t>-71,54; 62,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 239,34</t>
+          <t>31,7; 332,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 54,06</t>
+          <t>-59,51; 66,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 333,17</t>
+          <t>15,92; 252,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,22; 32,28</t>
+          <t>-54,52; 24,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,66; 224,94</t>
+          <t>47,04; 211,99</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,62</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,76</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,51</t>
+          <t>1,76; 10,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 17,48</t>
+          <t>3,81; 14,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 10,38</t>
+          <t>-3,34; 5,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,39</t>
+          <t>4,85; 17,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,67</t>
+          <t>0,46; 6,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 13,77</t>
+          <t>5,99; 14,01</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>123,77%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>189,81%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>14,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>168,83%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>123,77%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200,21%</t>
+          <t>171,69%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>179,03%</t>
+          <t>177,57%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 128,66</t>
+          <t>15,55; 371,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,47; 405,72</t>
+          <t>45,48; 512,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 361,18</t>
+          <t>-40,11; 128,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,75; 493,11</t>
+          <t>47,32; 430,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 161,11</t>
+          <t>3,67; 170,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,39; 327,6</t>
+          <t>86,31; 355,12</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,35</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,81</t>
+          <t>-0,89; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,42</t>
+          <t>1,92; 5,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,2</t>
+          <t>-1,47; 1,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,02</t>
+          <t>2,97; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,56</t>
+          <t>-0,87; 1,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,67</t>
+          <t>3,2; 5,99</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143,7%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-0,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>124,27%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148,7%</t>
+          <t>140,63%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134,9%</t>
+          <t>141,41%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 69,46</t>
+          <t>-24,82; 101,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,96; 238,36</t>
+          <t>49,44; 276,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 110,35</t>
+          <t>-36,12; 63,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54,99; 270,47</t>
+          <t>64,61; 262,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,23</t>
+          <t>-22,92; 51,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,41; 224,44</t>
+          <t>85,25; 228,75</t>
         </is>
       </c>
     </row>
